--- a/NLM.F.xlsx
+++ b/NLM.F.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDFAE1B-0DDE-4736-B95A-D48DB492331E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A459FC4-F050-46ED-9F20-D804D82397B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="5070" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{0050BF43-1F1D-40ED-B104-A6C0579DED4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{0050BF43-1F1D-40ED-B104-A6C0579DED4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3839,7 +3839,7 @@
         <v>266.57600000000002</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" ref="C18:F18" si="17">+E16+E17</f>
+        <f t="shared" ref="E18:F18" si="17">+E16+E17</f>
         <v>318.29699999999997</v>
       </c>
       <c r="F18" s="4">
